--- a/data/_training_log.xlsx
+++ b/data/_training_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -712,6 +712,74 @@
         <v>-69.77521299926272</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-11T16:57:48</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>b2daedcab</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>128</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LogisticRegression, RandomForestClassifier, XGBClassifier</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>123.7</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>./data/england/p4_modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>55.55544408103752</v>
+      </c>
+      <c r="L5" t="n">
+        <v>41.70808482086634</v>
+      </c>
+      <c r="M5" t="n">
+        <v>57.77777777777777</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.48941466413353</v>
+      </c>
+      <c r="O5" t="n">
+        <v>74.41219697492232</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-39.10469974392496</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>34.15122477508152</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-60.58173499540043</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/_training_log.xlsx
+++ b/data/_training_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,74 @@
         <v>-60.58173499540043</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-11T17:31:50</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>930b516ba</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>./data/england/p4_modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>40.18893456810256</v>
+      </c>
+      <c r="L6" t="n">
+        <v>40.18893456810256</v>
+      </c>
+      <c r="M6" t="n">
+        <v>46.46464646464646</v>
+      </c>
+      <c r="N6" t="n">
+        <v>46.46464646464646</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-50.63803714701597</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-50.63803714701597</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-63.20676058337337</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-63.20676058337337</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/_training_log.xlsx
+++ b/data/_training_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,6 +848,142 @@
         <v>-63.20676058337337</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-11T18:06:41</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>48f68b2f9</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>./data/england/p4_modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>40.02622325525955</v>
+      </c>
+      <c r="L7" t="n">
+        <v>40.02622325525955</v>
+      </c>
+      <c r="M7" t="n">
+        <v>46.46464646464646</v>
+      </c>
+      <c r="N7" t="n">
+        <v>46.46464646464646</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-50.43823901159817</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-50.43823901159817</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-55.1471159119458</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-55.1471159119458</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-11T18:16:24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>48f68b2f9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>./data/england/p4_modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>42.02721503953307</v>
+      </c>
+      <c r="L8" t="n">
+        <v>42.02721503953307</v>
+      </c>
+      <c r="M8" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="N8" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-42.64597380811845</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-42.64597380811845</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-69.77894380569109</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-69.77894380569109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
